--- a/data/siigeo_stations.xlsx
+++ b/data/siigeo_stations.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA231"/>
+  <dimension ref="A1:AA229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>Satelital</t>
+          <t>Satelital LEO</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr"/>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>Satelital</t>
+          <t>Satelital LEO</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr"/>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Episensor, DC to &gt;200 Hz,  20V differential full s</t>
+          <t>GS-1LF, 1 s, 365.3 V/m/s-Q330SR, gain 1, 100 sps,</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>GS-1LF, 1 s, 365.3 V/m/s-Q330SR, gain 1, 100 sps,</t>
+          <t>Episensor, DC to &gt;200 Hz,  20V differential full s</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -8804,12 +8804,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Episensor, DC to &gt;200 Hz,  20V differential full s</t>
+          <t>LK-307-115, DC to 200 Hz, 20Vp single-ended full s</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2023-04-27 15:00:00</t>
+          <t>2025-09-25 20:30:00</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8933,36 +8933,36 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ACELEROGRAFO, NANOMETRICS TITAN SERIAL: 000493</t>
+          <t>Titan, DC to 430 Hz, 20V differential full scale v</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2019-02-03 19:00:00</t>
-        </is>
-      </c>
-      <c r="Q66" s="2" t="inlineStr"/>
+          <t>2019-02-04 21:00:00</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>2599-12-31 23:59:59</t>
+        </is>
+      </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
           <t>Activa</t>
         </is>
       </c>
-      <c r="S66" s="2" t="inlineStr">
-        <is>
-          <t>Trigger</t>
-        </is>
-      </c>
+      <c r="S66" s="2" t="inlineStr"/>
       <c r="T66" s="2" t="inlineStr">
         <is>
           <t>Caseta</t>
         </is>
       </c>
-      <c r="U66" s="2" t="inlineStr"/>
-      <c r="V66" s="2" t="inlineStr">
-        <is>
-          <t>Visita</t>
-        </is>
-      </c>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>Celular</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr"/>
       <c r="W66" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>Descarga</t>
+          <t>Tiempo Real</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -14705,22 +14705,22 @@
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>CMG-5T, DC_100 s,  0.255 V/m/s**2, 4g clip level,</t>
+          <t>STS-2.5, 120s, 1500 V/m/s-Q330SR, gain 1, 100 sps,</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>2022-03-22 13:00:00</t>
+          <t>2016-08-04 16:37:00</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
         <is>
-          <t>2599-12-31 23:59:59</t>
+          <t>2025-08-31 23:59:59</t>
         </is>
       </c>
       <c r="R111" s="2" t="inlineStr">
@@ -14731,7 +14731,7 @@
       <c r="S111" s="2" t="inlineStr"/>
       <c r="T111" s="2" t="inlineStr">
         <is>
-          <t>Caseta</t>
+          <t>Bunker</t>
         </is>
       </c>
       <c r="U111" s="2" t="inlineStr">
@@ -14834,22 +14834,22 @@
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>STS-2.5, 120s, 1500 V/m/s-Q330SR, gain 1, 100 sps,</t>
+          <t>CMG-5T, DC_100 s,  0.255 V/m/s**2, 4g clip level,</t>
         </is>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>2016-08-04 16:37:00</t>
+          <t>2022-03-22 13:00:00</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>2025-08-31 23:59:59</t>
+          <t>2599-12-31 23:59:59</t>
         </is>
       </c>
       <c r="R112" s="2" t="inlineStr">
@@ -14860,7 +14860,7 @@
       <c r="S112" s="2" t="inlineStr"/>
       <c r="T112" s="2" t="inlineStr">
         <is>
-          <t>Bunker</t>
+          <t>Caseta</t>
         </is>
       </c>
       <c r="U112" s="2" t="inlineStr">
@@ -18676,22 +18676,22 @@
       </c>
       <c r="N142" s="2" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>RTcolt, 120 s, 2000 V/m/s-Q330SR, gain 1, 100 sps,</t>
+          <t>EPISENSOR 6341</t>
         </is>
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>2024-05-25 17:00:00</t>
+          <t>2014-09-09 05:00:00</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
         <is>
-          <t>2599-12-31 23:59:59</t>
+          <t>2600-01-01 05:00:00</t>
         </is>
       </c>
       <c r="R142" s="2" t="inlineStr">
@@ -18805,22 +18805,22 @@
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>EPISENSOR 6341</t>
+          <t>RTcolt, 120 s, 2000 V/m/s-Q330SR, gain 1, 100 sps,</t>
         </is>
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>2014-09-09 05:00:00</t>
+          <t>2024-05-25 17:00:00</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
         <is>
-          <t>2600-01-01 05:00:00</t>
+          <t>2599-12-31 23:59:59</t>
         </is>
       </c>
       <c r="R143" s="2" t="inlineStr">
@@ -21537,7 +21537,7 @@
       </c>
       <c r="U164" s="2" t="inlineStr">
         <is>
-          <t>Satelital</t>
+          <t>Satelital LEO</t>
         </is>
       </c>
       <c r="V164" s="2" t="inlineStr"/>
@@ -21666,7 +21666,7 @@
       </c>
       <c r="U165" s="2" t="inlineStr">
         <is>
-          <t>Satelital</t>
+          <t>Satelital LEO</t>
         </is>
       </c>
       <c r="V165" s="2" t="inlineStr"/>
@@ -22272,12 +22272,12 @@
       </c>
       <c r="N170" s="2" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
-          <t>RTcolt, 120 s, 2000 V/m/s-Q330SR, gain 1, 100 sps,</t>
+          <t>Episensor, DC to &gt;200 Hz,  20V differential full s</t>
         </is>
       </c>
       <c r="P170" s="2" t="inlineStr">
@@ -22401,12 +22401,12 @@
       </c>
       <c r="N171" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
-          <t>Episensor, DC to &gt;200 Hz,  20V differential full s</t>
+          <t>RTcolt, 120 s, 2000 V/m/s-Q330SR, gain 1, 100 sps,</t>
         </is>
       </c>
       <c r="P171" s="2" t="inlineStr">
@@ -25254,7 +25254,7 @@
       </c>
       <c r="U193" s="2" t="inlineStr">
         <is>
-          <t>Celular</t>
+          <t>Satelital LEO</t>
         </is>
       </c>
       <c r="V193" s="2" t="inlineStr"/>
@@ -25383,7 +25383,7 @@
       </c>
       <c r="U194" s="2" t="inlineStr">
         <is>
-          <t>Celular</t>
+          <t>Satelital LEO</t>
         </is>
       </c>
       <c r="V194" s="2" t="inlineStr"/>
@@ -25993,17 +25993,17 @@
       </c>
       <c r="N199" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
-          <t>Episensor, DC to &gt;200 Hz,  20V differential full s</t>
+          <t>CMG-6T, 1s-100Hz, 2400 V/m/s-Q330SR, gain 1, 100 s</t>
         </is>
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>2024-05-13 20:31:00</t>
+          <t>2021-11-09 12:05:00</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -26019,7 +26019,7 @@
       <c r="S199" s="2" t="inlineStr"/>
       <c r="T199" s="2" t="inlineStr">
         <is>
-          <t>Caseta</t>
+          <t>Bunker</t>
         </is>
       </c>
       <c r="U199" s="2" t="inlineStr">
@@ -26122,17 +26122,17 @@
       </c>
       <c r="N200" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
-          <t>CMG-6T, 1s-100Hz, 2400 V/m/s-Q330SR, gain 1, 100 s</t>
+          <t>Episensor, DC to &gt;200 Hz,  20V differential full s</t>
         </is>
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>2021-11-09 12:05:00</t>
+          <t>2024-05-13 20:31:00</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -26148,7 +26148,7 @@
       <c r="S200" s="2" t="inlineStr"/>
       <c r="T200" s="2" t="inlineStr">
         <is>
-          <t>Bunker</t>
+          <t>Caseta</t>
         </is>
       </c>
       <c r="U200" s="2" t="inlineStr">
@@ -27408,7 +27408,7 @@
       </c>
       <c r="N210" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O210" s="2" t="inlineStr">
@@ -27434,12 +27434,12 @@
       <c r="S210" s="2" t="inlineStr"/>
       <c r="T210" s="2" t="inlineStr">
         <is>
-          <t>Borehole</t>
+          <t>Caseta</t>
         </is>
       </c>
       <c r="U210" s="2" t="inlineStr">
         <is>
-          <t>Satelital LEO</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="V210" s="2" t="inlineStr"/>
@@ -27537,7 +27537,7 @@
       </c>
       <c r="N211" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O211" s="2" t="inlineStr">
@@ -27563,12 +27563,12 @@
       <c r="S211" s="2" t="inlineStr"/>
       <c r="T211" s="2" t="inlineStr">
         <is>
-          <t>Caseta</t>
+          <t>Borehole</t>
         </is>
       </c>
       <c r="U211" s="2" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Satelital LEO</t>
         </is>
       </c>
       <c r="V211" s="2" t="inlineStr"/>
@@ -28698,17 +28698,17 @@
       </c>
       <c r="N220" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O220" s="2" t="inlineStr">
         <is>
-          <t>Strong Motion TSM-1 038, Unity Gain-Q330HR, gain 1</t>
+          <t>CMG-6T, 1s-100Hz, 2400 V/m/s-Q330SR, gain 1, 100 s</t>
         </is>
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>2020-02-13 19:28:33</t>
+          <t>2021-12-02 17:00:00</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -28827,17 +28827,17 @@
       </c>
       <c r="N221" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="O221" s="2" t="inlineStr">
         <is>
-          <t>CMG-6T, 1s-100Hz, 2400 V/m/s-Q330SR, gain 1, 100 s</t>
+          <t>Strong Motion TSM-1 038, Unity Gain-Q330HR, gain 1</t>
         </is>
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>2021-12-02 17:00:00</t>
+          <t>2020-02-13 19:28:33</t>
         </is>
       </c>
       <c r="Q221" s="2" t="inlineStr">
@@ -29544,37 +29544,37 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>YOT</t>
+          <t>YPLC</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>YOTOCO</t>
+          <t>YOPAL</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>3.983</t>
+          <t>5.397</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>-76.345</t>
+          <t>-72.380</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>1059.0</t>
+          <t>696.0</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>VALLE DEL CAUCA</t>
+          <t>CASANARE</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>YOTOCO</t>
+          <t>YOPAL</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -29604,7 +29604,7 @@
       </c>
       <c r="M227" s="2" t="inlineStr">
         <is>
-          <t>MIGUEL LIZARAZO</t>
+          <t>ANGEL DANIEL AGUDELO</t>
         </is>
       </c>
       <c r="N227" s="2" t="inlineStr">
@@ -29614,12 +29614,12 @@
       </c>
       <c r="O227" s="2" t="inlineStr">
         <is>
-          <t>RTcolt, 120 s, 2000 V/m/s-Q330SR, gain 1, 100 sps,</t>
+          <t>CMG40T, 60 s, 2000 V/m/s-DM-24 Mk3 Fixed Gain, gai</t>
         </is>
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>2020-10-14 14:30:00</t>
+          <t>2021-04-22 00:00:00</t>
         </is>
       </c>
       <c r="Q227" s="2" t="inlineStr">
@@ -29640,7 +29640,7 @@
       </c>
       <c r="U227" s="2" t="inlineStr">
         <is>
-          <t>Satelital</t>
+          <t>Satelital LEO</t>
         </is>
       </c>
       <c r="V227" s="2" t="inlineStr"/>
@@ -29666,44 +29666,44 @@
       </c>
       <c r="AA227" s="2" t="inlineStr">
         <is>
-          <t>2011-12-09</t>
+          <t>2017-03-05</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>YOT</t>
+          <t>YPLC</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>YOTOCO</t>
+          <t>YOPAL</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>3.983</t>
+          <t>5.397</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>-76.345</t>
+          <t>-72.380</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>1059.0</t>
+          <t>696.0</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>VALLE DEL CAUCA</t>
+          <t>CASANARE</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>YOTOCO</t>
+          <t>YOPAL</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -29733,7 +29733,7 @@
       </c>
       <c r="M228" s="2" t="inlineStr">
         <is>
-          <t>MIGUEL LIZARAZO</t>
+          <t>ANGEL DANIEL AGUDELO</t>
         </is>
       </c>
       <c r="N228" s="2" t="inlineStr">
@@ -29748,12 +29748,12 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>2018-10-09 15:38:00</t>
+          <t>2024-05-09 12:00:00</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
         <is>
-          <t>2005-12-31 23:59:59</t>
+          <t>2599-12-31 23:59:59</t>
         </is>
       </c>
       <c r="R228" s="2" t="inlineStr">
@@ -29769,7 +29769,7 @@
       </c>
       <c r="U228" s="2" t="inlineStr">
         <is>
-          <t>Satelital</t>
+          <t>Satelital LEO</t>
         </is>
       </c>
       <c r="V228" s="2" t="inlineStr"/>
@@ -29795,44 +29795,44 @@
       </c>
       <c r="AA228" s="2" t="inlineStr">
         <is>
-          <t>2011-12-09</t>
+          <t>2017-03-05</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>YPLC</t>
+          <t>ZAR</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>YOPAL</t>
+          <t>ZARAGOZA</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>5.397</t>
+          <t>7.492</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>-72.380</t>
+          <t>-74.858</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>696.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>CASANARE</t>
+          <t>ANTIOQUIA</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>YOPAL</t>
+          <t>ZARAGOZA</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -29847,12 +29847,12 @@
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>HIBRIDA</t>
+          <t>RSNC</t>
         </is>
       </c>
       <c r="K229" s="2" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L229" s="2" t="inlineStr">
@@ -29862,7 +29862,7 @@
       </c>
       <c r="M229" s="2" t="inlineStr">
         <is>
-          <t>ANGEL DANIEL AGUDELO</t>
+          <t>HELBER GARCIA</t>
         </is>
       </c>
       <c r="N229" s="2" t="inlineStr">
@@ -29872,12 +29872,12 @@
       </c>
       <c r="O229" s="2" t="inlineStr">
         <is>
-          <t>CMG40T, 60 s, 2000 V/m/s-DM-24 Mk3 Fixed Gain, gai</t>
+          <t>STS-2.5, 120s, 1500 V/m/s-Q330SR, gain 1, 100 sps,</t>
         </is>
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>2021-04-22 00:00:00</t>
+          <t>2014-08-04 00:00:00</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -29923,264 +29923,6 @@
         </is>
       </c>
       <c r="AA229" s="2" t="inlineStr">
-        <is>
-          <t>2017-03-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="2" t="inlineStr">
-        <is>
-          <t>YPLC</t>
-        </is>
-      </c>
-      <c r="B230" s="2" t="inlineStr">
-        <is>
-          <t>YOPAL</t>
-        </is>
-      </c>
-      <c r="C230" s="2" t="inlineStr">
-        <is>
-          <t>5.397</t>
-        </is>
-      </c>
-      <c r="D230" s="2" t="inlineStr">
-        <is>
-          <t>-72.380</t>
-        </is>
-      </c>
-      <c r="E230" s="2" t="inlineStr">
-        <is>
-          <t>696.0</t>
-        </is>
-      </c>
-      <c r="F230" s="2" t="inlineStr">
-        <is>
-          <t>CASANARE</t>
-        </is>
-      </c>
-      <c r="G230" s="2" t="inlineStr">
-        <is>
-          <t>YOPAL</t>
-        </is>
-      </c>
-      <c r="H230" s="2" t="inlineStr">
-        <is>
-          <t>SERVICIO GEOLOGICO COLOMBIANO</t>
-        </is>
-      </c>
-      <c r="I230" s="2" t="inlineStr">
-        <is>
-          <t>ACTIVA</t>
-        </is>
-      </c>
-      <c r="J230" s="2" t="inlineStr">
-        <is>
-          <t>HIBRIDA</t>
-        </is>
-      </c>
-      <c r="K230" s="2" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L230" s="2" t="inlineStr">
-        <is>
-          <t>JUAN MANUEL SOLANO</t>
-        </is>
-      </c>
-      <c r="M230" s="2" t="inlineStr">
-        <is>
-          <t>ANGEL DANIEL AGUDELO</t>
-        </is>
-      </c>
-      <c r="N230" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="O230" s="2" t="inlineStr">
-        <is>
-          <t>CMG-5T, DC_100 s,  0.255 V/m/s**2, 4g clip level,</t>
-        </is>
-      </c>
-      <c r="P230" s="2" t="inlineStr">
-        <is>
-          <t>2024-05-09 12:00:00</t>
-        </is>
-      </c>
-      <c r="Q230" s="2" t="inlineStr">
-        <is>
-          <t>2599-12-31 23:59:59</t>
-        </is>
-      </c>
-      <c r="R230" s="2" t="inlineStr">
-        <is>
-          <t>Activa</t>
-        </is>
-      </c>
-      <c r="S230" s="2" t="inlineStr"/>
-      <c r="T230" s="2" t="inlineStr">
-        <is>
-          <t>Bunker</t>
-        </is>
-      </c>
-      <c r="U230" s="2" t="inlineStr">
-        <is>
-          <t>Celular</t>
-        </is>
-      </c>
-      <c r="V230" s="2" t="inlineStr"/>
-      <c r="W230" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="X230" s="2" t="inlineStr">
-        <is>
-          <t>Permanente</t>
-        </is>
-      </c>
-      <c r="Y230" s="2" t="inlineStr">
-        <is>
-          <t>Tiempo Real</t>
-        </is>
-      </c>
-      <c r="Z230" s="2" t="inlineStr">
-        <is>
-          <t>SERVICIO GEOLOGICO COLOMBIANO</t>
-        </is>
-      </c>
-      <c r="AA230" s="2" t="inlineStr">
-        <is>
-          <t>2017-03-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="2" t="inlineStr">
-        <is>
-          <t>ZAR</t>
-        </is>
-      </c>
-      <c r="B231" s="2" t="inlineStr">
-        <is>
-          <t>ZARAGOZA</t>
-        </is>
-      </c>
-      <c r="C231" s="2" t="inlineStr">
-        <is>
-          <t>7.492</t>
-        </is>
-      </c>
-      <c r="D231" s="2" t="inlineStr">
-        <is>
-          <t>-74.858</t>
-        </is>
-      </c>
-      <c r="E231" s="2" t="inlineStr">
-        <is>
-          <t>200.0</t>
-        </is>
-      </c>
-      <c r="F231" s="2" t="inlineStr">
-        <is>
-          <t>ANTIOQUIA</t>
-        </is>
-      </c>
-      <c r="G231" s="2" t="inlineStr">
-        <is>
-          <t>ZARAGOZA</t>
-        </is>
-      </c>
-      <c r="H231" s="2" t="inlineStr">
-        <is>
-          <t>SERVICIO GEOLOGICO COLOMBIANO</t>
-        </is>
-      </c>
-      <c r="I231" s="2" t="inlineStr">
-        <is>
-          <t>ACTIVA</t>
-        </is>
-      </c>
-      <c r="J231" s="2" t="inlineStr">
-        <is>
-          <t>RSNC</t>
-        </is>
-      </c>
-      <c r="K231" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L231" s="2" t="inlineStr">
-        <is>
-          <t>JUAN MANUEL SOLANO</t>
-        </is>
-      </c>
-      <c r="M231" s="2" t="inlineStr">
-        <is>
-          <t>HELBER GARCIA</t>
-        </is>
-      </c>
-      <c r="N231" s="2" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="O231" s="2" t="inlineStr">
-        <is>
-          <t>STS-2.5, 120s, 1500 V/m/s-Q330SR, gain 1, 100 sps,</t>
-        </is>
-      </c>
-      <c r="P231" s="2" t="inlineStr">
-        <is>
-          <t>2014-08-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q231" s="2" t="inlineStr">
-        <is>
-          <t>2599-12-31 23:59:59</t>
-        </is>
-      </c>
-      <c r="R231" s="2" t="inlineStr">
-        <is>
-          <t>Activa</t>
-        </is>
-      </c>
-      <c r="S231" s="2" t="inlineStr"/>
-      <c r="T231" s="2" t="inlineStr">
-        <is>
-          <t>Bunker</t>
-        </is>
-      </c>
-      <c r="U231" s="2" t="inlineStr">
-        <is>
-          <t>Celular</t>
-        </is>
-      </c>
-      <c r="V231" s="2" t="inlineStr"/>
-      <c r="W231" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="X231" s="2" t="inlineStr">
-        <is>
-          <t>Permanente</t>
-        </is>
-      </c>
-      <c r="Y231" s="2" t="inlineStr">
-        <is>
-          <t>Tiempo Real</t>
-        </is>
-      </c>
-      <c r="Z231" s="2" t="inlineStr">
-        <is>
-          <t>SERVICIO GEOLOGICO COLOMBIANO</t>
-        </is>
-      </c>
-      <c r="AA231" s="2" t="inlineStr">
         <is>
           <t>2011-08-25</t>
         </is>

--- a/data/siigeo_stations.xlsx
+++ b/data/siigeo_stations.xlsx
@@ -4036,7 +4036,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2023-02-20 13:00:00</t>
+          <t>2025-09-29 18:15:00</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>CMG-5T, DC_100 s,  0.255 V/m/s**2, 4g clip level,</t>
+          <t>LK-307-115, DC to 200 Hz, 20Vp single-ended full s</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2023-02-10 13:00:00</t>
+          <t>2025-09-30 18:39:00</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8572,11 +8572,7 @@
         </is>
       </c>
       <c r="V63" s="2" t="inlineStr"/>
-      <c r="W63" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
+      <c r="W63" s="2" t="inlineStr"/>
       <c r="X63" s="2" t="inlineStr">
         <is>
           <t>Permanente</t>
@@ -18151,7 +18147,7 @@
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>PAOLA ANDREA ATAPUMA</t>
+          <t>LUISA CASTILLO</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">

--- a/data/siigeo_stations.xlsx
+++ b/data/siigeo_stations.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>OMAR MERCADO</t>
+          <t>DANIEL RUIZ</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>OMAR MERCADO</t>
+          <t>DANIEL RUIZ</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>OMAR MERCADO</t>
+          <t>DANIEL RUIZ</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>OMAR MERCADO</t>
+          <t>MIGUEL LIZARAZO</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>OMAR MERCADO</t>
+          <t>MIGUEL LIZARAZO</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>ANGEL DANIEL AGUDELO</t>
+          <t>HELBER GARCIA</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>ANGEL DANIEL AGUDELO</t>
+          <t>HELBER GARCIA</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>OMAR MERCADO</t>
+          <t>VIVIANA DIONICIO</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>OMAR MERCADO</t>
+          <t>VIVIANA DIONICIO</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>OMAR MERCADO</t>
+          <t>LUISA CASTILLO</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>OMAR MERCADO</t>
+          <t>VIVIANA DIONICIO</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>OMAR MERCADO</t>
+          <t>VIVIANA DIONICIO</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>OMAR MERCADO</t>
+          <t>VIVIANA DIONICIO</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -12656,7 +12656,7 @@
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>PAOLA ANDREA ATAPUMA</t>
+          <t>ELIZABETH MAZO</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>PAOLA ANDREA ATAPUMA</t>
+          <t>ELIZABETH MAZO</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>PAOLA ANDREA ATAPUMA</t>
+          <t>ELIZABETH MAZO</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -13297,7 +13297,7 @@
       <c r="L100" s="2" t="inlineStr"/>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>OMAR MERCADO</t>
+          <t>DANIEL RUIZ</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -13414,7 +13414,7 @@
       <c r="L101" s="2" t="inlineStr"/>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>OMAR MERCADO</t>
+          <t>DANIEL RUIZ</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -13539,7 +13539,7 @@
       <c r="L102" s="2" t="inlineStr"/>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>OMAR MERCADO</t>
+          <t>DANIEL RUIZ</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -13664,7 +13664,7 @@
       <c r="L103" s="2" t="inlineStr"/>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>OMAR MERCADO</t>
+          <t>DANIEL RUIZ</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -13789,7 +13789,7 @@
       <c r="L104" s="2" t="inlineStr"/>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>OMAR MERCADO</t>
+          <t>DANIEL RUIZ</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -13914,7 +13914,7 @@
       <c r="L105" s="2" t="inlineStr"/>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>OMAR MERCADO</t>
+          <t>DANIEL RUIZ</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>OMAR MERCADO</t>
+          <t>MIGUEL LIZARAZO</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -16095,7 +16095,7 @@
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>PAOLA ANDREA ATAPUMA</t>
+          <t>HELBER GARCIA</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -16224,7 +16224,7 @@
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>OMAR MERCADO</t>
+          <t>DANIEL RUIZ</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -16740,7 +16740,7 @@
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>OMAR MERCADO</t>
+          <t>DANIEL RUIZ</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -21743,7 +21743,7 @@
       <c r="L166" s="2" t="inlineStr"/>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>OMAR MERCADO</t>
+          <t>DANIEL RUIZ</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -21868,7 +21868,7 @@
       <c r="L167" s="2" t="inlineStr"/>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>OMAR MERCADO</t>
+          <t>DANIEL RUIZ</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
@@ -27004,7 +27004,7 @@
       </c>
       <c r="M207" s="2" t="inlineStr">
         <is>
-          <t>OMAR MERCADO</t>
+          <t>MIGUEL LIZARAZO</t>
         </is>
       </c>
       <c r="N207" s="2" t="inlineStr">
